--- a/GreenhillOboarding.xlsx
+++ b/GreenhillOboarding.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EDF999B-0AF4-4D06-B4F8-63812B399499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{4EDF999B-0AF4-4D06-B4F8-63812B399499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69DA405D-E624-4B26-B878-DEE76241D982}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19305" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="236">
   <si>
     <t xml:space="preserve">  HOW TO FILL IN THIS TEMPLATE</t>
   </si>
@@ -714,6 +714,18 @@
   </si>
   <si>
     <t>Principal Himne</t>
+  </si>
+  <si>
+    <t>EC2 Email</t>
+  </si>
+  <si>
+    <t>Lafras</t>
+  </si>
+  <si>
+    <t>Fritz</t>
+  </si>
+  <si>
+    <t>info.galoon@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1003,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1045,21 +1057,6 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1141,6 +1138,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1160,6 +1175,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1638,18 +1657,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="4" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
@@ -1688,7 +1707,7 @@
       <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="47" t="s">
         <v>230</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -1823,31 +1842,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -1870,7 +1889,7 @@
       <c r="A6" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="46" t="s">
         <v>226</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1986,7 +2005,7 @@
   <sheetPr>
     <tabColor rgb="FFFFB703"/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -1995,95 +2014,98 @@
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
+    <col min="10" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:22" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+    </row>
+    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-    </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+    </row>
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-    </row>
-    <row r="5" spans="1:21" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+    </row>
+    <row r="5" spans="1:22" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>63</v>
       </c>
@@ -2115,44 +2137,47 @@
         <v>72</v>
       </c>
       <c r="K5" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="L5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="M5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="N5" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="O5" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="P5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="Q5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="R5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="R5" s="18" t="s">
+      <c r="S5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="T5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="T5" s="18" t="s">
+      <c r="U5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="U5" s="18" t="s">
+      <c r="V5" s="18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="41">
+    <row r="6" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="36">
         <v>2505160523086</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -2167,57 +2192,58 @@
       <c r="F6" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="19" t="s">
         <v>111</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="27"/>
+      <c r="L6" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="M6" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="O6" s="24" t="s">
+      <c r="N6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="P6" s="24" t="s">
+      <c r="Q6" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="28">
+      <c r="R6" s="23">
         <v>55201039894</v>
       </c>
-      <c r="R6" s="24" t="s">
+      <c r="S6" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="S6" s="34">
+      <c r="T6" s="29">
         <v>9203170118088</v>
       </c>
-      <c r="T6" s="24">
+      <c r="U6" s="19">
         <v>2</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="V6" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
+    <row r="7" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37">
         <v>2204025282084</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="20" t="s">
         <v>89</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -2229,60 +2255,61 @@
       <c r="E7" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="G7" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="46" t="s">
+      <c r="J7" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="41"/>
+      <c r="L7" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="M7" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="25" t="s">
+      <c r="N7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="Q7" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="Q7" s="29">
+      <c r="R7" s="24">
         <v>424204550</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="S7" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="35">
+      <c r="T7" s="30">
         <v>8801165150080</v>
       </c>
-      <c r="T7" s="25">
+      <c r="U7" s="20">
         <v>3</v>
       </c>
-      <c r="U7" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43">
+      <c r="V7" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38">
         <v>2201030584082</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="21" t="s">
         <v>91</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -2297,57 +2324,58 @@
       <c r="F8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="21" t="s">
         <v>113</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="27"/>
+      <c r="L8" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="M8" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="O8" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="P8" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="P8" s="26" t="s">
+      <c r="Q8" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="Q8" s="30">
+      <c r="R8" s="25">
         <v>912589175</v>
       </c>
-      <c r="R8" s="26" t="s">
+      <c r="S8" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="S8" s="36">
+      <c r="T8" s="31">
         <v>9401270325088</v>
       </c>
-      <c r="T8" s="26">
+      <c r="U8" s="21">
         <v>3</v>
       </c>
-      <c r="U8" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
+      <c r="V8" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="37">
         <v>2503065359086</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="20" t="s">
         <v>93</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -2362,57 +2390,58 @@
       <c r="F9" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="20" t="s">
         <v>113</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="27"/>
+      <c r="L9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="M9" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="N9" s="32" t="s">
+      <c r="O9" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="P9" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="Q9" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="Q9" s="29">
+      <c r="R9" s="24">
         <v>912589175</v>
       </c>
-      <c r="R9" s="25" t="s">
+      <c r="S9" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="S9" s="37">
+      <c r="T9" s="32">
         <v>9401270325088</v>
       </c>
-      <c r="T9" s="25">
+      <c r="U9" s="20">
         <v>4</v>
       </c>
-      <c r="U9" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44">
+      <c r="V9" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="39">
         <v>2211156377088</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="21" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="16" t="s">
@@ -2427,57 +2456,58 @@
       <c r="F10" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="21" t="s">
         <v>114</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="41"/>
+      <c r="L10" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="L10" s="50" t="s">
+      <c r="M10" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="26" t="s">
+      <c r="N10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="Q10" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="R10" s="25">
         <v>754178400</v>
       </c>
-      <c r="R10" s="26" t="s">
+      <c r="S10" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="S10" s="38">
+      <c r="T10" s="33">
         <v>9104075064080</v>
       </c>
-      <c r="T10" s="26">
+      <c r="U10" s="21">
         <v>2</v>
       </c>
-      <c r="U10" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47">
+      <c r="V10" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="42">
         <v>2407120307082</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="43" t="s">
         <v>171</v>
       </c>
       <c r="C11" s="16" t="s">
@@ -2492,51 +2522,52 @@
       <c r="F11" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="35" t="s">
         <v>114</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="46" t="s">
+      <c r="J11" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="41"/>
+      <c r="L11" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="50" t="s">
+      <c r="M11" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="26" t="s">
+      <c r="N11" s="16"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="26" t="s">
+      <c r="Q11" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="Q11" s="30">
+      <c r="R11" s="25">
         <v>754178400</v>
       </c>
-      <c r="R11" s="26" t="s">
+      <c r="S11" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="S11" s="49">
+      <c r="T11" s="44">
         <v>9104075064080</v>
       </c>
-      <c r="T11" s="48">
+      <c r="U11" s="43">
         <v>3</v>
       </c>
-      <c r="U11" s="16"/>
-    </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43">
+      <c r="V11" s="16"/>
+    </row>
+    <row r="12" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="38">
         <v>2406300437081</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="21" t="s">
         <v>184</v>
       </c>
       <c r="C12" s="16" t="s">
@@ -2551,57 +2582,58 @@
       <c r="F12" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="21" t="s">
         <v>115</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="26" t="s">
+      <c r="K12" s="28"/>
+      <c r="L12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="P12" s="26" t="s">
+      <c r="Q12" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="Q12" s="30">
+      <c r="R12" s="25">
         <v>916649819</v>
       </c>
-      <c r="R12" s="26" t="s">
+      <c r="S12" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="S12" s="38">
+      <c r="T12" s="33">
         <v>9211275050080</v>
       </c>
-      <c r="T12" s="26">
+      <c r="U12" s="21">
         <v>3</v>
       </c>
-      <c r="U12" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42">
+      <c r="V12" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="37">
         <v>2312015507087</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="20" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -2613,60 +2645,61 @@
       <c r="E13" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="20" t="s">
         <v>116</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="28"/>
+      <c r="L13" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="L13" s="33" t="s">
+      <c r="M13" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N13" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O13" s="25" t="s">
+      <c r="N13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="P13" s="25" t="s">
+      <c r="Q13" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="Q13" s="29">
+      <c r="R13" s="24">
         <v>7165897</v>
       </c>
-      <c r="R13" s="25" t="s">
+      <c r="S13" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="S13" s="35">
+      <c r="T13" s="30">
         <v>8407220010085</v>
       </c>
-      <c r="T13" s="29">
+      <c r="U13" s="24">
         <v>2</v>
       </c>
-      <c r="U13" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43">
+      <c r="V13" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38">
         <v>2306266148088</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C14" s="16" t="s">
@@ -2681,57 +2714,58 @@
       <c r="F14" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="21" t="s">
         <v>117</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="28"/>
+      <c r="L14" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="L14" s="33" t="s">
+      <c r="M14" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="26" t="s">
+      <c r="N14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="P14" s="26" t="s">
+      <c r="Q14" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="Q14" s="30">
+      <c r="R14" s="25">
         <v>7693818</v>
       </c>
-      <c r="R14" s="26" t="s">
+      <c r="S14" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="S14" s="38">
+      <c r="T14" s="33">
         <v>8504275017088</v>
       </c>
-      <c r="T14" s="30">
+      <c r="U14" s="25">
         <v>4</v>
       </c>
-      <c r="U14" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
+      <c r="V14" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="37">
         <v>2508015620081</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="20" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -2746,57 +2780,58 @@
       <c r="F15" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="20" t="s">
         <v>118</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="33" t="s">
+      <c r="J15" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="28"/>
+      <c r="L15" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="L15" s="33" t="s">
+      <c r="M15" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="25" t="s">
+      <c r="N15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="P15" s="25" t="s">
+      <c r="Q15" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="Q15" s="29">
+      <c r="R15" s="24">
         <v>198477457</v>
       </c>
-      <c r="R15" s="25" t="s">
+      <c r="S15" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="S15" s="35">
+      <c r="T15" s="30">
         <v>9105025024082</v>
       </c>
-      <c r="T15" s="25">
+      <c r="U15" s="20">
         <v>2</v>
       </c>
-      <c r="U15" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43">
+      <c r="V15" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38">
         <v>2307215736080</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="21" t="s">
         <v>101</v>
       </c>
       <c r="C16" s="16" t="s">
@@ -2811,57 +2846,58 @@
       <c r="F16" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="21" t="s">
         <v>119</v>
       </c>
       <c r="I16" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="J16" s="33" t="s">
+      <c r="J16" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="K16" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N16" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O16" s="26" t="s">
+      <c r="K16" s="28"/>
+      <c r="L16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="P16" s="26" t="s">
+      <c r="Q16" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="Q16" s="30">
+      <c r="R16" s="25">
         <v>24004278285</v>
       </c>
-      <c r="R16" s="26" t="s">
+      <c r="S16" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="S16" s="38">
+      <c r="T16" s="33">
         <v>9709270112086</v>
       </c>
-      <c r="T16" s="26">
+      <c r="U16" s="21">
         <v>3</v>
       </c>
-      <c r="U16" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42">
+      <c r="V16" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="37">
         <v>2301270371081</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="20" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="16" t="s">
@@ -2876,57 +2912,58 @@
       <c r="F17" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="20" t="s">
         <v>120</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="J17" s="33" t="s">
+      <c r="J17" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="K17" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="25" t="s">
+      <c r="K17" s="28"/>
+      <c r="L17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="P17" s="25" t="s">
+      <c r="Q17" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="Q17" s="29">
+      <c r="R17" s="24">
         <v>915065195</v>
       </c>
-      <c r="R17" s="25" t="s">
+      <c r="S17" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="S17" s="35">
+      <c r="T17" s="30">
         <v>9206100035082</v>
       </c>
-      <c r="T17" s="25">
+      <c r="U17" s="20">
         <v>2</v>
       </c>
-      <c r="U17" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
+      <c r="V17" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="21" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -2941,57 +2978,58 @@
       <c r="F18" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="H18" s="21" t="s">
         <v>121</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="J18" s="33" t="s">
+      <c r="J18" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="28"/>
+      <c r="L18" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="L18" s="33" t="s">
+      <c r="M18" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="26" t="s">
+      <c r="N18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="P18" s="26" t="s">
+      <c r="Q18" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="Q18" s="30">
+      <c r="R18" s="25">
         <v>651706560</v>
       </c>
-      <c r="R18" s="26" t="s">
+      <c r="S18" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="S18" s="38">
+      <c r="T18" s="33">
         <v>9008225010085</v>
       </c>
-      <c r="T18" s="26">
+      <c r="U18" s="21">
         <v>3</v>
       </c>
-      <c r="U18" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45">
+      <c r="V18" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="40">
         <v>2109015397083</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="22" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="16" t="s">
@@ -3003,97 +3041,96 @@
       <c r="E19" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="H19" s="27" t="s">
+      <c r="H19" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="J19" s="46" t="s">
+      <c r="J19" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K19" s="41"/>
+      <c r="L19" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="L19" s="33" t="s">
+      <c r="M19" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="N19" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="N19" s="33" t="s">
+      <c r="O19" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="O19" s="27" t="s">
+      <c r="P19" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="P19" s="27" t="s">
+      <c r="Q19" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="Q19" s="31">
+      <c r="R19" s="26">
         <v>934646670</v>
       </c>
-      <c r="R19" s="27" t="s">
+      <c r="S19" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="S19" s="39">
+      <c r="T19" s="34">
         <v>8106165203081</v>
       </c>
-      <c r="T19" s="27">
-        <v>5</v>
-      </c>
-      <c r="U19" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>5</v>
+      <c r="U19" s="22">
+        <v>5</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>123456</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>5</v>
+        <v>233</v>
+      </c>
+      <c r="G20" s="16">
+        <v>123456</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>235</v>
       </c>
       <c r="I20" s="16"/>
-      <c r="J20" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="16" t="s">
+      <c r="J20" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="28"/>
+      <c r="L20" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P20" s="16" t="s">
@@ -3105,17 +3142,20 @@
       <c r="R20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="16" t="s">
+      <c r="S20" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U20" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V20" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>5</v>
       </c>
@@ -3143,22 +3183,20 @@
       <c r="I21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="16" t="s">
+      <c r="J21" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="28"/>
+      <c r="L21" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P21" s="16" t="s">
@@ -3170,17 +3208,20 @@
       <c r="R21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="16" t="s">
+      <c r="S21" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U21" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V21" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>5</v>
       </c>
@@ -3208,22 +3249,20 @@
       <c r="I22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="16" t="s">
+      <c r="J22" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="28"/>
+      <c r="L22" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P22" s="16" t="s">
@@ -3235,17 +3274,20 @@
       <c r="R22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="16" t="s">
+      <c r="S22" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U22" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V22" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>5</v>
       </c>
@@ -3273,22 +3315,20 @@
       <c r="I23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="16" t="s">
+      <c r="J23" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="28"/>
+      <c r="L23" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P23" s="16" t="s">
@@ -3300,17 +3340,20 @@
       <c r="R23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="16" t="s">
+      <c r="S23" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U23" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V23" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>5</v>
       </c>
@@ -3338,22 +3381,20 @@
       <c r="I24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J24" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="16" t="s">
+      <c r="J24" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="28"/>
+      <c r="L24" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P24" s="16" t="s">
@@ -3365,17 +3406,20 @@
       <c r="R24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S24" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="16" t="s">
+      <c r="S24" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U24" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V24" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>5</v>
       </c>
@@ -3403,22 +3447,20 @@
       <c r="I25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L25" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N25" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O25" s="16" t="s">
+      <c r="J25" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="K25" s="28"/>
+      <c r="L25" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P25" s="16" t="s">
@@ -3430,17 +3472,20 @@
       <c r="R25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S25" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="T25" s="16" t="s">
+      <c r="S25" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T25" s="28" t="s">
         <v>5</v>
       </c>
       <c r="U25" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>5</v>
       </c>
@@ -3471,19 +3516,17 @@
       <c r="J26" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K26" s="16"/>
       <c r="L26" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="16" t="s">
+      <c r="N26" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="28" t="s">
         <v>5</v>
       </c>
       <c r="P26" s="16" t="s">
@@ -3504,8 +3547,11 @@
       <c r="U26" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V26" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>5</v>
       </c>
@@ -3536,9 +3582,7 @@
       <c r="J27" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K27" s="16"/>
       <c r="L27" s="16" t="s">
         <v>5</v>
       </c>
@@ -3569,8 +3613,11 @@
       <c r="U27" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V27" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>5</v>
       </c>
@@ -3601,9 +3648,7 @@
       <c r="J28" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K28" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K28" s="16"/>
       <c r="L28" s="16" t="s">
         <v>5</v>
       </c>
@@ -3634,8 +3679,11 @@
       <c r="U28" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V28" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>5</v>
       </c>
@@ -3666,9 +3714,7 @@
       <c r="J29" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K29" s="16"/>
       <c r="L29" s="16" t="s">
         <v>5</v>
       </c>
@@ -3699,8 +3745,11 @@
       <c r="U29" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V29" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>5</v>
       </c>
@@ -3731,9 +3780,7 @@
       <c r="J30" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K30" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K30" s="16"/>
       <c r="L30" s="16" t="s">
         <v>5</v>
       </c>
@@ -3764,8 +3811,11 @@
       <c r="U30" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V30" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>5</v>
       </c>
@@ -3796,9 +3846,7 @@
       <c r="J31" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K31" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K31" s="16"/>
       <c r="L31" s="16" t="s">
         <v>5</v>
       </c>
@@ -3829,8 +3877,11 @@
       <c r="U31" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V31" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>5</v>
       </c>
@@ -3861,9 +3912,7 @@
       <c r="J32" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K32" s="16"/>
       <c r="L32" s="16" t="s">
         <v>5</v>
       </c>
@@ -3894,8 +3943,11 @@
       <c r="U32" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V32" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>5</v>
       </c>
@@ -3926,9 +3978,7 @@
       <c r="J33" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K33" s="16"/>
       <c r="L33" s="16" t="s">
         <v>5</v>
       </c>
@@ -3959,8 +4009,11 @@
       <c r="U33" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V33" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>5</v>
       </c>
@@ -3991,9 +4044,7 @@
       <c r="J34" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K34" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K34" s="16"/>
       <c r="L34" s="16" t="s">
         <v>5</v>
       </c>
@@ -4024,8 +4075,11 @@
       <c r="U34" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V34" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
@@ -4056,9 +4110,7 @@
       <c r="J35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K35" s="16"/>
       <c r="L35" s="16" t="s">
         <v>5</v>
       </c>
@@ -4089,8 +4141,11 @@
       <c r="U35" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V35" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>5</v>
       </c>
@@ -4121,9 +4176,7 @@
       <c r="J36" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K36" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K36" s="16"/>
       <c r="L36" s="16" t="s">
         <v>5</v>
       </c>
@@ -4154,8 +4207,11 @@
       <c r="U36" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V36" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>5</v>
       </c>
@@ -4186,9 +4242,7 @@
       <c r="J37" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K37" s="16"/>
       <c r="L37" s="16" t="s">
         <v>5</v>
       </c>
@@ -4219,8 +4273,11 @@
       <c r="U37" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V37" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>5</v>
       </c>
@@ -4251,9 +4308,7 @@
       <c r="J38" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="16" t="s">
-        <v>5</v>
-      </c>
+      <c r="K38" s="16"/>
       <c r="L38" s="16" t="s">
         <v>5</v>
       </c>
@@ -4282,15 +4337,21 @@
         <v>5</v>
       </c>
       <c r="U38" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="V38" s="16" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:V3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H20" r:id="rId1" xr:uid="{05CB287E-3E81-4B4A-A82D-24C1ACE31B16}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
